--- a/2026_code/resultado/carga 2026-04-20 10-18-54/carga 2026-04-20 10-18-54 parte 6.xlsx
+++ b/2026_code/resultado/carga 2026-04-20 10-18-54/carga 2026-04-20 10-18-54 parte 6.xlsx
@@ -19215,6 +19215,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19287,6 +19292,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19359,6 +19369,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19431,6 +19446,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19503,6 +19523,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19575,6 +19600,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19647,6 +19677,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19719,6 +19754,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19791,6 +19831,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19863,6 +19908,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>V23</t>
@@ -19935,6 +19985,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20007,6 +20062,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20079,6 +20139,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20151,6 +20216,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20223,6 +20293,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20295,6 +20370,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20367,6 +20447,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20439,6 +20524,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20511,6 +20601,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20583,6 +20678,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20655,6 +20755,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20727,6 +20832,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20799,6 +20909,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20871,6 +20986,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>V23</t>
@@ -20943,6 +21063,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>V23</t>
@@ -21015,6 +21140,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>V23</t>
@@ -21087,6 +21217,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>V23</t>
@@ -21159,6 +21294,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>V23</t>
@@ -21231,6 +21371,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>V23</t>
@@ -21303,6 +21448,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>V23</t>
@@ -21375,6 +21525,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>V23</t>
@@ -21447,6 +21602,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>V23</t>
@@ -21519,6 +21679,11 @@
           <t>Cecyte 26 Colola</t>
         </is>
       </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>V23</t>
@@ -21589,6 +21754,11 @@
       <c r="C278" t="inlineStr">
         <is>
           <t>Cecyte 26 Colola</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>MATUTINO</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
